--- a/src/assets/郵寄明細報表.xlsx
+++ b/src/assets/郵寄明細報表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>客戶代號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,6 +34,10 @@
   </si>
   <si>
     <t>負責業務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯絡人(承辦)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -91,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -107,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -447,34 +454,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="44.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="3"/>
+    <col min="2" max="3" width="20.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="44.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
